--- a/r5-ELGA-MOPED-126-changes-for-pysische-anwesenheit/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-126-changes-for-pysische-anwesenheit/StructureDefinition-SVCCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-21T06:07:01+00:00</t>
+    <t>2024-10-25T08:29:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-126-changes-for-pysische-anwesenheit/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-126-changes-for-pysische-anwesenheit/StructureDefinition-SVCCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T08:29:24+00:00</t>
+    <t>2024-10-29T09:40:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -463,10 +463,10 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>Coverage.extension:RezeptgebbefreitExtension</t>
-  </si>
-  <si>
-    <t>RezeptgebbefreitExtension</t>
+    <t>Coverage.extension:rezeptgebbefreitExtension</t>
+  </si>
+  <si>
+    <t>rezeptgebbefreitExtension</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {http://example.org/StructureDefinition/ecard-anspruch-rezeptgebbefreit}
@@ -481,10 +481,10 @@
 verankert und werden meistens errechnet (z.B. für Heilbehelfe und Hilfsmittel).</t>
   </si>
   <si>
-    <t>Coverage.extension:KostenanteilbefreitExtension</t>
-  </si>
-  <si>
-    <t>KostenanteilbefreitExtension</t>
+    <t>Coverage.extension:kostenanteilbefreitExtension</t>
+  </si>
+  <si>
+    <t>kostenanteilbefreitExtension</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {http://example.org/StructureDefinition/ecard-anspruch-kostenanteilbefreit}
@@ -1855,7 +1855,7 @@
   <cols>
     <col min="1" max="1" width="61.02734375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="53.57421875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="27.53125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="27.390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>

--- a/r5-ELGA-MOPED-126-changes-for-pysische-anwesenheit/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-126-changes-for-pysische-anwesenheit/StructureDefinition-SVCCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T09:40:57+00:00</t>
+    <t>2024-10-29T10:51:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
